--- a/survey_templates/031_event_visitor_survey--survey_templates.xlsx
+++ b/survey_templates/031_event_visitor_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'event_visitor_survey'}</t>
+          <t>event_visitor_survey</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Event Visitor Survey'}</t>
+          <t>Event Visitor Survey</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'event_feedback_form'}</t>
+          <t>event_feedback_form</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Event Feedback Form'}</t>
+          <t>Event Feedback Form</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'feedback_form'}</t>
+          <t>feedback_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Feedback Form'}</t>
+          <t>Feedback Form</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'visitor_survey'}</t>
+          <t>visitor_survey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Visitor Survey'}</t>
+          <t>Visitor Survey</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'event_survey'}</t>
+          <t>event_survey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Event Survey'}</t>
+          <t>Event Survey</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'attended_alone'}</t>
+          <t>attended_alone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Attended alone'}</t>
+          <t>Attended alone</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'attended_with_friends'}</t>
+          <t>attended_with_friends</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Attended with friends'}</t>
+          <t>Attended with friends</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'attended_with_family'}</t>
+          <t>attended_with_family</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Attended with family'}</t>
+          <t>Attended with family</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'attended_with_colleagues'}</t>
+          <t>attended_with_colleagues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Attended with colleagues'}</t>
+          <t>Attended with colleagues</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_times'}</t>
+          <t>1-2_times</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '1-2 times'}</t>
+          <t>1-2 times</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'3-5_times'}</t>
+          <t>3-5_times</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '3-5 times'}</t>
+          <t>3-5 times</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'6-10_times'}</t>
+          <t>6-10_times</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '6-10 times'}</t>
+          <t>6-10 times</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_10_times'}</t>
+          <t>more_than_10_times</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'More than 10 times'}</t>
+          <t>More than 10 times</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Neither satisfied nor dissatisfied'}</t>
+          <t>Neither satisfied nor dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'online_event'}</t>
+          <t>online_event</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Online event'}</t>
+          <t>Online event</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'in_person_event'}</t>
+          <t>in_person_event</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'In person event'}</t>
+          <t>In person event</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'offline_promotion'}</t>
+          <t>offline_promotion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Offline promotion'}</t>
+          <t>Offline promotion</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_times'}</t>
+          <t>1-2_times</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': '1-2 times'}</t>
+          <t>1-2 times</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'3-5_times'}</t>
+          <t>3-5_times</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': '3-5 times'}</t>
+          <t>3-5 times</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'6-10_times'}</t>
+          <t>6-10_times</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': '6-10 times'}</t>
+          <t>6-10 times</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_10_times'}</t>
+          <t>more_than_10_times</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'More than 10 times'}</t>
+          <t>More than 10 times</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'attended_alone'}</t>
+          <t>attended_alone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Attended alone'}</t>
+          <t>Attended alone</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'attended_with_friends'}</t>
+          <t>attended_with_friends</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Attended with friends'}</t>
+          <t>Attended with friends</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'attended_with_family'}</t>
+          <t>attended_with_family</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Attended with family'}</t>
+          <t>Attended with family</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'attended_with_colleagues'}</t>
+          <t>attended_with_colleagues</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Attended with colleagues'}</t>
+          <t>Attended with colleagues</t>
         </is>
       </c>
     </row>
